--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:09</t>
+    <t xml:space="preserve">2026-10-05 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1320017.12</v>
+        <v>1320017.13</v>
       </c>
     </row>
     <row r="3">
